--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,14 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D31FEF63-51CE-464B-AEC9-AC65A8C3A39C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A065C609-3CAE-AE4F-A89F-2F2B93C34B12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="1560" windowWidth="27080" windowHeight="16440" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
+    <workbookView xWindow="4520" yWindow="980" windowWidth="27080" windowHeight="16440" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="used" sheetId="1" r:id="rId1"/>
+    <sheet name="to_add " sheetId="2" r:id="rId2"/>
+    <sheet name="deprecated" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
   <si>
     <t>HERV-L68</t>
   </si>
@@ -47,9 +49,6 @@
     <t>ERV-3.Lambda.L</t>
   </si>
   <si>
-    <t>erv_derived_repeat</t>
-  </si>
-  <si>
     <t>excluded</t>
   </si>
   <si>
@@ -278,15 +277,6 @@
     <t>Iotaretrovirus</t>
   </si>
   <si>
-    <t>LOR-1</t>
-  </si>
-  <si>
-    <t>ERVR-1.Theta.LOR1</t>
-  </si>
-  <si>
-    <t>ERV-1.Theta</t>
-  </si>
-  <si>
     <t>HERV-V</t>
   </si>
   <si>
@@ -294,12 +284,6 @@
   </si>
   <si>
     <t>human endogenous retrovirus V</t>
-  </si>
-  <si>
-    <t>PRIMA-X</t>
-  </si>
-  <si>
-    <t>ERV-1.Zeta.primax</t>
   </si>
   <si>
     <t>sequenceID</t>
@@ -477,7 +461,47 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -798,106 +822,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35878EA-9699-8640-B361-4136681AAF96}">
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" customWidth="1"/>
     <col min="4" max="4" width="46.83203125" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="N1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="I2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="K2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -905,7 +930,7 @@
         <v>2825129</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -916,40 +941,40 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>42</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="H3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="I3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>40</v>
-      </c>
       <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -957,7 +982,7 @@
         <v>2825129</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q3">
         <v>3</v>
@@ -968,49 +993,48 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>71</v>
+        <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>73</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>2</v>
+        <v>9</v>
+      </c>
+      <c r="Q4">
+        <v>4</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>
@@ -1018,51 +1042,44 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>75</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>76</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>13</v>
+        <v>75</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="F5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>18</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2">
-        <v>28397686</v>
+        <v>45</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>1</v>
+        <v>9</v>
+      </c>
+      <c r="Q5">
+        <v>4</v>
       </c>
       <c r="R5" s="2" t="b">
         <v>1</v>
@@ -1070,50 +1087,48 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
-      <c r="O6" s="2">
-        <v>28397686</v>
-      </c>
+      <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q6" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" s="2" t="b">
@@ -1122,50 +1137,46 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>2</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="G7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>29</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="J7" s="4"/>
       <c r="K7" s="2" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2">
-        <v>28397686</v>
-      </c>
+      <c r="O7" s="2"/>
       <c r="P7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q7" s="2">
+        <v>9</v>
+      </c>
+      <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7" s="2" t="b">
@@ -1174,648 +1185,60 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>74</v>
+        <v>14</v>
       </c>
       <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
       <c r="I8" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="J8" s="4"/>
       <c r="K8" s="2" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>46</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9" s="4"/>
-      <c r="K9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>3</v>
-      </c>
-      <c r="R9" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E10" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q10">
-        <v>1</v>
-      </c>
-      <c r="R10" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11" s="4"/>
-      <c r="K11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>3</v>
-      </c>
-      <c r="R11" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J12" s="4"/>
-      <c r="K12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q12">
-        <v>1</v>
-      </c>
-      <c r="R12" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="P13" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q13">
-        <v>4</v>
-      </c>
-      <c r="R13" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G14" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="2">
-        <v>20</v>
-      </c>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2">
-        <v>31167914</v>
-      </c>
-      <c r="P14" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>1</v>
-      </c>
-      <c r="R14" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2">
-        <v>20</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2">
-        <v>31167914</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>1</v>
-      </c>
-      <c r="R15" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q16">
-        <v>5</v>
-      </c>
-      <c r="R16" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s">
-        <v>5</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q17">
-        <v>1</v>
-      </c>
-      <c r="R17" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" t="s">
-        <v>5</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4"/>
-      <c r="K18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q18">
-        <v>1</v>
-      </c>
-      <c r="R18" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G19" t="s">
-        <v>5</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J19" s="4"/>
-      <c r="K19" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>2</v>
-      </c>
-      <c r="R19" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G20" t="s">
-        <v>5</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="J20" s="4"/>
-      <c r="K20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q20">
-        <v>1</v>
-      </c>
-      <c r="R20" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R20">
-    <sortCondition ref="G2:G20"/>
-    <sortCondition ref="H2:H20"/>
-    <sortCondition ref="I2:I20"/>
-    <sortCondition ref="J2:J20"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q17">
+    <sortCondition ref="G2:G17"/>
+    <sortCondition ref="H2:H17"/>
+    <sortCondition ref="I2:I17"/>
   </sortState>
-  <conditionalFormatting sqref="Q2:Q9">
-    <cfRule type="colorScale" priority="13">
+  <conditionalFormatting sqref="Q2:Q3 Q5">
+    <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1826,13 +1249,13 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G20">
-    <cfRule type="containsText" dxfId="0" priority="12" operator="containsText" text="excluded">
+  <conditionalFormatting sqref="G2:G5">
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q10">
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="Q4">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1843,7 +1266,503 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11">
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:G8">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q7">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q8">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F84D856-EE91-3040-A544-A187B8BBFACA}">
+  <dimension ref="A1:R8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="2">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>1</v>
+      </c>
+      <c r="R3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>1</v>
+      </c>
+      <c r="R4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G5" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M6" s="2">
+        <v>20</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>1</v>
+      </c>
+      <c r="R6" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M7" s="2">
+        <v>20</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>1</v>
+      </c>
+      <c r="R7" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J8" s="4"/>
+      <c r="K8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>3</v>
+      </c>
+      <c r="R8" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2:G8">
+    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q5">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1855,43 +1774,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q12:Q13">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q15">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q14">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q16">
+  <conditionalFormatting sqref="Q7">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1903,8 +1786,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q17">
-    <cfRule type="colorScale" priority="5">
+  <conditionalFormatting sqref="Q6">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1912,30 +1795,6 @@
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q18:Q19">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q20">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -1963,6 +1822,302 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q2:Q4 Q8">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DAEDAF5-BD77-644B-A293-87D1BB2B812D}">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A1" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2">
+        <v>5</v>
+      </c>
+      <c r="R2" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>2</v>
+      </c>
+      <c r="R3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>2</v>
+      </c>
+      <c r="R4" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G2:G3">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G4">
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q4">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A065C609-3CAE-AE4F-A89F-2F2B93C34B12}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC72FA2-3B63-8B42-B434-0B95483E9C13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4520" yWindow="980" windowWidth="27080" windowHeight="16440" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
+    <workbookView xWindow="3840" yWindow="8620" windowWidth="27080" windowHeight="16440" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>
   <sheets>
     <sheet name="used" sheetId="1" r:id="rId1"/>
@@ -35,16 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="103">
-  <si>
-    <t>HERV-L68</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.68</t>
-  </si>
-  <si>
-    <t>human endogenous retrovirus L68</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="95">
   <si>
     <t>ERV-3.Lambda.L</t>
   </si>
@@ -148,9 +139,6 @@
     <t>ERV-1.Zeta.W9P.P</t>
   </si>
   <si>
-    <t>accepted</t>
-  </si>
-  <si>
     <t>Zetaretrovirus</t>
   </si>
   <si>
@@ -230,18 +218,6 @@
   </si>
   <si>
     <t>endogenous retrovirus Le</t>
-  </si>
-  <si>
-    <t>ERV-L47</t>
-  </si>
-  <si>
-    <t>ERV-3.Lambda.47</t>
-  </si>
-  <si>
-    <t>endogenous retrovirus L47</t>
-  </si>
-  <si>
-    <t>Sigmaretrovirus</t>
   </si>
   <si>
     <t>HERV-1</t>
@@ -390,7 +366,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -421,12 +397,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -440,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -456,7 +426,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -822,107 +791,107 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35878EA-9699-8640-B361-4136681AAF96}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:R6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="46.83203125" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
     <col min="9" max="9" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -930,7 +899,7 @@
         <v>2825129</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>3</v>
@@ -941,40 +910,40 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>37</v>
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -982,7 +951,7 @@
         <v>2825129</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q3">
         <v>3</v>
@@ -993,45 +962,45 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G4" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q4">
         <v>4</v>
@@ -1042,41 +1011,41 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q5">
         <v>4</v>
@@ -1087,155 +1056,59 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J6" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="K6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="L6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
       <c r="P6" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="4"/>
-      <c r="K7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8" s="2" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q17">
-    <sortCondition ref="G2:G17"/>
-    <sortCondition ref="H2:H17"/>
-    <sortCondition ref="I2:I17"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q16">
+    <sortCondition ref="G2:G16"/>
+    <sortCondition ref="H2:H16"/>
+    <sortCondition ref="I2:I16"/>
   </sortState>
   <conditionalFormatting sqref="Q2:Q3 Q5">
     <cfRule type="colorScale" priority="19">
@@ -1302,33 +1175,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6:G8">
+  <conditionalFormatting sqref="G6">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="excluded">
       <formula>NOT(ISERROR(SEARCH("excluded",G6)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q7">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q8">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1345,96 +1194,96 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="J2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="K2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1442,7 +1291,7 @@
         <v>28397686</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q2" s="2">
         <v>1</v>
@@ -1453,40 +1302,40 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
@@ -1494,7 +1343,7 @@
         <v>28397686</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q3" s="2">
         <v>1</v>
@@ -1505,40 +1354,40 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="K4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1546,7 +1395,7 @@
         <v>28397686</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q4" s="2">
         <v>1</v>
@@ -1557,41 +1406,41 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q5">
         <v>1</v>
@@ -1602,40 +1451,40 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="J6" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="K6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M6" s="2">
         <v>20</v>
@@ -1645,7 +1494,7 @@
         <v>31167914</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q6" s="2">
         <v>1</v>
@@ -1656,40 +1505,40 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="K7" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="L7" s="2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="M7" s="2">
         <v>20</v>
@@ -1699,7 +1548,7 @@
         <v>31167914</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Q7" s="2">
         <v>1</v>
@@ -1710,44 +1559,44 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="J8" s="4"/>
       <c r="K8" s="2" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q8" s="2">
         <v>3</v>
@@ -1845,102 +1694,102 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="P1" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="J2" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q2">
         <v>5</v>
@@ -1951,46 +1800,46 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>7</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q3" s="2">
         <v>2</v>
@@ -2001,44 +1850,44 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Q4" s="2">
         <v>2</v>

--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC72FA2-3B63-8B42-B434-0B95483E9C13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33C9450-4FB4-BB45-97DD-A4E5EC8EBCE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="8620" windowWidth="27080" windowHeight="16440" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
+    <workbookView xWindow="940" yWindow="500" windowWidth="27380" windowHeight="10840" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>
   <sheets>
     <sheet name="used" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="137">
   <si>
     <t>ERV-3.Lambda.L</t>
   </si>
@@ -79,18 +79,9 @@
     <t>Gammaretrovirus</t>
   </si>
   <si>
-    <t>HERVT1</t>
-  </si>
-  <si>
-    <t>AncRecon</t>
-  </si>
-  <si>
     <t>majority_consensus</t>
   </si>
   <si>
-    <t>YES</t>
-  </si>
-  <si>
     <t>HERV-T2</t>
   </si>
   <si>
@@ -100,9 +91,6 @@
     <t>human endogenous retrovirus T2</t>
   </si>
   <si>
-    <t>HERVT2</t>
-  </si>
-  <si>
     <t>HERV-T3</t>
   </si>
   <si>
@@ -112,21 +100,12 @@
     <t>human endogenous retrovirus T3</t>
   </si>
   <si>
-    <t>HERVT3</t>
-  </si>
-  <si>
     <t>HERV-24b</t>
   </si>
   <si>
-    <t>ERV-1.Theta.24.b</t>
-  </si>
-  <si>
     <t>human endogenous retrovirus 24b</t>
   </si>
   <si>
-    <t>Theta.Lb</t>
-  </si>
-  <si>
     <t>Thetaretrovirus</t>
   </si>
   <si>
@@ -166,30 +145,18 @@
     <t>HERV-K-HML6-1a</t>
   </si>
   <si>
-    <t>ERV-2.Beta.K6.1a</t>
-  </si>
-  <si>
     <t>HERV-K-HML6</t>
   </si>
   <si>
-    <t>ERV-2.Beta.K6</t>
-  </si>
-  <si>
     <t>II</t>
   </si>
   <si>
     <t>Betaretrovirus</t>
   </si>
   <si>
-    <t>Archaeobeta</t>
-  </si>
-  <si>
     <t>HERV-K-HML6-1b</t>
   </si>
   <si>
-    <t>ERV-2.Beta.K6.1b</t>
-  </si>
-  <si>
     <t>ERV-Lb4</t>
   </si>
   <si>
@@ -256,9 +223,6 @@
     <t>HERV-V</t>
   </si>
   <si>
-    <t>ERV-1.Theta.V</t>
-  </si>
-  <si>
     <t>human endogenous retrovirus V</t>
   </si>
   <si>
@@ -320,13 +284,175 @@
   </si>
   <si>
     <t>endogenous retrovirus K HML6 type 1b</t>
+  </si>
+  <si>
+    <t>ERV-1.Eta.E</t>
+  </si>
+  <si>
+    <t>HARLEQUIN</t>
+  </si>
+  <si>
+    <t>ERV-1.Eta.E.HQ</t>
+  </si>
+  <si>
+    <t>length</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.24</t>
+  </si>
+  <si>
+    <t>HERV-W-SG1</t>
+  </si>
+  <si>
+    <t>HERV-W-SG2</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.W</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.W.SG1</t>
+  </si>
+  <si>
+    <t>ERV-1.Zeta.W9P.W.SG2</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus W SG1</t>
+  </si>
+  <si>
+    <t>human endogenous retrovirus W SG2</t>
+  </si>
+  <si>
+    <t>Rhoretrovirus</t>
+  </si>
+  <si>
+    <t>ERV-1.Rho.V</t>
+  </si>
+  <si>
+    <t>ERV-1.Rho</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.Archeo.6</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.Archeo.6.1a</t>
+  </si>
+  <si>
+    <t>ERV-2.Beta.Archeo.6.1b</t>
+  </si>
+  <si>
+    <t>REV</t>
+  </si>
+  <si>
+    <t>Archaeo</t>
+  </si>
+  <si>
+    <t>legacy_name</t>
+  </si>
+  <si>
+    <t>legacy_full_name</t>
+  </si>
+  <si>
+    <t>major_clade</t>
+  </si>
+  <si>
+    <t>minor_clade</t>
+  </si>
+  <si>
+    <t>Gamma-Eta</t>
+  </si>
+  <si>
+    <t>Sigma-Lambda</t>
+  </si>
+  <si>
+    <t>Alpha-Beta</t>
+  </si>
+  <si>
+    <t>reference_role</t>
+  </si>
+  <si>
+    <t>reference_status</t>
+  </si>
+  <si>
+    <t>derivation_method</t>
+  </si>
+  <si>
+    <t>canonical</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>consensus</t>
+  </si>
+  <si>
+    <t>ancestral_reconstruction</t>
+  </si>
+  <si>
+    <t>represented_form</t>
+  </si>
+  <si>
+    <t>reference_completeness</t>
+  </si>
+  <si>
+    <t>fragment_extent</t>
+  </si>
+  <si>
+    <t>proviral_genome</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>architecture_level</t>
+  </si>
+  <si>
+    <t>coding_level</t>
+  </si>
+  <si>
+    <t>validation_level</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>ERV-1.Theta.24b</t>
+  </si>
+  <si>
+    <t>representative_locus</t>
+  </si>
+  <si>
+    <t>fragmentary</t>
+  </si>
+  <si>
+    <t>envelope</t>
+  </si>
+  <si>
+    <t>internal</t>
+  </si>
+  <si>
+    <t>classification_basis</t>
+  </si>
+  <si>
+    <t>published_phylogeny</t>
+  </si>
+  <si>
+    <t>repeat_family</t>
+  </si>
+  <si>
+    <t>published_sequence_group</t>
+  </si>
+  <si>
+    <t>provisional_placement</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -365,8 +491,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -397,6 +529,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5FC79"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -410,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -426,11 +564,128 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -791,326 +1046,1307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D35878EA-9699-8640-B361-4136681AAF96}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.5" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="4" max="4" width="32.6640625" customWidth="1"/>
-    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="3" max="3" width="15.5" customWidth="1"/>
+    <col min="4" max="4" width="41.5" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="19.33203125" customWidth="1"/>
+    <col min="10" max="10" width="19.5" customWidth="1"/>
+    <col min="11" max="11" width="21.1640625" customWidth="1"/>
+    <col min="14" max="16" width="10.83203125" style="13"/>
+    <col min="17" max="17" width="23.83203125" style="13" customWidth="1"/>
+    <col min="18" max="18" width="19.6640625" customWidth="1"/>
+    <col min="20" max="20" width="16.6640625" customWidth="1"/>
+    <col min="21" max="21" width="23" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="23" max="23" width="18.1640625" customWidth="1"/>
+    <col min="26" max="26" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="S1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="T1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="U1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="W1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="X1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="Z1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N2" s="12"/>
+      <c r="O2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S2" s="2"/>
+      <c r="T2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V2" s="2"/>
+      <c r="W2" s="14">
+        <v>1</v>
+      </c>
+      <c r="X2" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y2" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="2" t="s">
+    <row r="3" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3" t="s">
+      <c r="F3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2">
-        <v>2825129</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q2">
-        <v>3</v>
-      </c>
-      <c r="R2" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="J3" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M3" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N3" s="12"/>
+      <c r="O3" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P3" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q3" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="T3" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V3" s="2"/>
+      <c r="W3" s="14">
+        <v>0</v>
+      </c>
+      <c r="X3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" s="2" t="s">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="F4" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3">
-        <v>2825129</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q3">
-        <v>3</v>
-      </c>
-      <c r="R3" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="J4" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M4" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N4" s="12"/>
+      <c r="O4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P4" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q4" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S4" s="2"/>
+      <c r="T4" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V4" s="2"/>
+      <c r="W4" s="14">
+        <v>0</v>
+      </c>
+      <c r="X4" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2">
+        <v>28397686</v>
+      </c>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>12</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="P4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q4">
-        <v>4</v>
-      </c>
-      <c r="R4" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q5">
-        <v>4</v>
-      </c>
-      <c r="R5" s="2" t="b">
-        <v>1</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="L5" s="2"/>
+      <c r="M5" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N5" s="12"/>
+      <c r="O5" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q5" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T5" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W5" s="14">
+        <v>1</v>
+      </c>
+      <c r="X5" s="14">
+        <v>3</v>
+      </c>
+      <c r="Y5" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" ht="17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>53</v>
+        <v>61</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M6" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N6" s="12"/>
+      <c r="O6" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P6" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q6" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="T6" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="W6" s="14">
+        <v>1</v>
+      </c>
+      <c r="X6" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y6" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="s">
+      <c r="F7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>87</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M7" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N7" s="12"/>
+      <c r="O7" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P7" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q7" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="T7" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V7" s="2"/>
+      <c r="W7" s="14">
+        <v>1</v>
+      </c>
+      <c r="X7" s="14">
         <v>2</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="Y7" s="14">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M8" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N8" s="12"/>
+      <c r="O8" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P8" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q8" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S8" s="2"/>
+      <c r="T8" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V8" s="2"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
+      <c r="X8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M9" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N9" s="12"/>
+      <c r="O9" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P9" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q9" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S9" s="2"/>
+      <c r="T9" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V9" s="2"/>
+      <c r="W9" s="14">
+        <v>1</v>
+      </c>
+      <c r="X9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L10" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M10" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N10" s="12"/>
+      <c r="O10" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P10" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q10" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S10" s="2"/>
+      <c r="T10" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="W10" s="14">
+        <v>0</v>
+      </c>
+      <c r="X10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2">
+        <v>2825129</v>
+      </c>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M11" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N11" s="12"/>
+      <c r="O11" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P11" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q11" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="S11" s="2"/>
+      <c r="T11" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="W11" s="14">
+        <v>0</v>
+      </c>
+      <c r="X11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2">
+        <v>2825129</v>
+      </c>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N12" s="12"/>
+      <c r="O12" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P12" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q12" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="S12" s="2"/>
+      <c r="T12" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V12" s="2"/>
+      <c r="W12" s="14">
+        <v>1</v>
+      </c>
+      <c r="X12" s="14">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M13" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N13" s="12"/>
+      <c r="O13" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P13" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q13" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S13" s="2">
+        <v>20</v>
+      </c>
+      <c r="T13" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V13" s="2"/>
+      <c r="W13" s="14">
+        <v>0</v>
+      </c>
+      <c r="X13" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="2"/>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="M14" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N14" s="12"/>
+      <c r="O14" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P14" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q14" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="S14" s="2">
+        <v>20</v>
+      </c>
+      <c r="T14" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="W14" s="14">
+        <v>0</v>
+      </c>
+      <c r="X14" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2">
+        <v>31167914</v>
+      </c>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="K15" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="L15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M15" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="N15" s="12"/>
+      <c r="O15" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="P15" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q15" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="S15" s="2"/>
+      <c r="T15" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="V15" s="2"/>
+      <c r="W15" s="14">
+        <v>1</v>
+      </c>
+      <c r="X15" s="14">
+        <v>2</v>
+      </c>
+      <c r="Y15" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q16">
-    <sortCondition ref="G2:G16"/>
-    <sortCondition ref="H2:H16"/>
-    <sortCondition ref="I2:I16"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:V15">
+    <sortCondition ref="J2:J15"/>
+    <sortCondition ref="K2:K15"/>
+    <sortCondition ref="L2:L15"/>
+    <sortCondition ref="A2:A15"/>
   </sortState>
-  <conditionalFormatting sqref="Q2:Q3 Q5">
+  <conditionalFormatting sqref="G3:H5">
+    <cfRule type="containsText" dxfId="14" priority="65" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G6:H6">
+    <cfRule type="containsText" dxfId="13" priority="51" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G6)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:H2 J2">
+    <cfRule type="containsText" dxfId="12" priority="45" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:H11">
+    <cfRule type="containsText" dxfId="11" priority="41" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G8)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:H7">
+    <cfRule type="containsText" dxfId="10" priority="43" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G12:H13">
+    <cfRule type="containsText" dxfId="9" priority="35" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G12)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14:H14">
+    <cfRule type="containsText" dxfId="8" priority="33" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G14)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15:H15">
+    <cfRule type="containsText" dxfId="7" priority="32" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",G15)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J3">
+    <cfRule type="containsText" dxfId="6" priority="29" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",J3)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J4">
+    <cfRule type="containsText" dxfId="5" priority="28" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",J4)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M1:N1">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O1">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q1">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O15">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2:P4">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q2">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P5">
     <cfRule type="colorScale" priority="19">
       <colorScale>
         <cfvo type="min"/>
@@ -1122,9 +2358,64 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G5">
-    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
+  <conditionalFormatting sqref="Q5">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P6:P15">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6:Q11 Q15">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q4">
@@ -1133,37 +2424,85 @@
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q3">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U1">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V1">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2:T15">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1:AC1">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W1:Y1">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1175,9 +2514,45 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G6">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G6)))</formula>
+  <conditionalFormatting sqref="W2:W15">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y15">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q12">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J5:J15">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",J5)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1186,69 +2561,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F84D856-EE91-3040-A544-A187B8BBFACA}">
-  <dimension ref="A1:R8"/>
+  <dimension ref="A1:AB2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="O1" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="P1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="R1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="S1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="T1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="V1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="W1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>92</v>
+      <c r="X1" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y1" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z1" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>126</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1262,356 +2667,160 @@
         <v>9</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" t="s">
-        <v>1</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="K2" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" s="4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M2" s="12"/>
+      <c r="N2" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="O2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="P2" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2">
+      <c r="S2" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="T2" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2">
         <v>28397686</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>1</v>
-      </c>
-      <c r="R2" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2">
-        <v>28397686</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>1</v>
-      </c>
-      <c r="R3" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2">
-        <v>28397686</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>1</v>
-      </c>
-      <c r="R4" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G5" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M6" s="2">
-        <v>20</v>
-      </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2">
-        <v>31167914</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>1</v>
-      </c>
-      <c r="R6" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="M7" s="2">
-        <v>20</v>
-      </c>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2">
-        <v>31167914</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>1</v>
-      </c>
-      <c r="R7" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="J8" s="4"/>
-      <c r="K8" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>3</v>
-      </c>
-      <c r="R8" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="X2" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="14">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="G2:G8">
-    <cfRule type="containsText" dxfId="2" priority="16" operator="containsText" text="excluded">
-      <formula>NOT(ISERROR(SEARCH("excluded",G2)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q5">
+  <conditionalFormatting sqref="F2:G2">
+    <cfRule type="containsText" dxfId="3" priority="18" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",F2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2">
+    <cfRule type="containsText" dxfId="2" priority="17" operator="containsText" text="excluded">
+      <formula>NOT(ISERROR(SEARCH("excluded",I2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N2">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O2">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P2">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S2">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T2">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Y2:Z2">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L1:M1">
     <cfRule type="colorScale" priority="9">
       <colorScale>
         <cfvo type="min"/>
@@ -1623,7 +2832,31 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q7">
+  <conditionalFormatting sqref="O1">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N1">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P1">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -1635,19 +2868,55 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q6">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q1">
+  <conditionalFormatting sqref="S1">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T1">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U1">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AB1">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X1:Z1">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1656,30 +2925,6 @@
         <color rgb="FF63BE7B"/>
         <color rgb="FFFFEB84"/>
         <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q4 Q8">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
@@ -1694,75 +2939,75 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q1" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="R1" s="7" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -1777,7 +3022,7 @@
         <v>3</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>4</v>
@@ -1800,22 +3045,22 @@
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="G3" t="s">
         <v>1</v>
@@ -1827,7 +3072,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>4</v>
@@ -1850,16 +3095,16 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>0</v>
@@ -1878,7 +3123,7 @@
       </c>
       <c r="J4" s="4"/>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>5</v>

--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33C9450-4FB4-BB45-97DD-A4E5EC8EBCE3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BA77EA-EEEA-4048-A67C-4739AF19EE4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27380" windowHeight="10840" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>

--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3BA77EA-EEEA-4048-A67C-4739AF19EE4A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895E8C8F-3ECD-E046-A189-EBA3B96E6B05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27380" windowHeight="10840" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>
@@ -498,7 +498,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -529,12 +529,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5FC79"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -548,7 +542,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -564,7 +558,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1058,8 +1051,8 @@
     <col min="8" max="8" width="19.33203125" customWidth="1"/>
     <col min="10" max="10" width="19.5" customWidth="1"/>
     <col min="11" max="11" width="21.1640625" customWidth="1"/>
-    <col min="14" max="16" width="10.83203125" style="13"/>
-    <col min="17" max="17" width="23.83203125" style="13" customWidth="1"/>
+    <col min="14" max="16" width="10.83203125" style="12"/>
+    <col min="17" max="17" width="23.83203125" style="12" customWidth="1"/>
     <col min="18" max="18" width="19.6640625" customWidth="1"/>
     <col min="20" max="20" width="16.6640625" customWidth="1"/>
     <col min="21" max="21" width="23" customWidth="1"/>
@@ -1093,10 +1086,10 @@
       <c r="H1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="10" t="s">
         <v>106</v>
       </c>
       <c r="K1" s="7" t="s">
@@ -1108,16 +1101,16 @@
       <c r="M1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="Q1" s="9" t="s">
         <v>112</v>
       </c>
       <c r="R1" s="7" t="s">
@@ -1126,22 +1119,22 @@
       <c r="S1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="9" t="s">
         <v>118</v>
       </c>
       <c r="V1" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>124</v>
       </c>
       <c r="Z1" s="7" t="s">
@@ -1161,7 +1154,7 @@
       <c r="A2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -1197,34 +1190,34 @@
       <c r="M2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N2" s="12"/>
-      <c r="O2" s="14" t="s">
+      <c r="N2" s="11"/>
+      <c r="O2" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q2" s="14" t="s">
+      <c r="Q2" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S2" s="2"/>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V2" s="2"/>
-      <c r="W2" s="14">
-        <v>1</v>
-      </c>
-      <c r="X2" s="14">
+      <c r="W2" s="13">
+        <v>1</v>
+      </c>
+      <c r="X2" s="13">
         <v>3</v>
       </c>
-      <c r="Y2" s="14">
+      <c r="Y2" s="13">
         <v>1</v>
       </c>
       <c r="Z2" s="2"/>
@@ -1272,34 +1265,34 @@
       <c r="M3" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N3" s="12"/>
-      <c r="O3" s="14" t="s">
+      <c r="N3" s="11"/>
+      <c r="O3" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P3" s="14" t="s">
+      <c r="P3" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q3" s="14" t="s">
+      <c r="Q3" s="13" t="s">
         <v>116</v>
       </c>
       <c r="R3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="S3" s="2"/>
-      <c r="T3" s="14" t="s">
+      <c r="T3" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V3" s="2"/>
-      <c r="W3" s="14">
+      <c r="W3" s="13">
         <v>0</v>
       </c>
-      <c r="X3" s="14">
+      <c r="X3" s="13">
         <v>0</v>
       </c>
-      <c r="Y3" s="14">
+      <c r="Y3" s="13">
         <v>0</v>
       </c>
       <c r="Z3" s="2"/>
@@ -1349,34 +1342,34 @@
       <c r="M4" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N4" s="12"/>
-      <c r="O4" s="14" t="s">
+      <c r="N4" s="11"/>
+      <c r="O4" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P4" s="14" t="s">
+      <c r="P4" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q4" s="14" t="s">
+      <c r="Q4" s="13" t="s">
         <v>116</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>14</v>
       </c>
       <c r="S4" s="2"/>
-      <c r="T4" s="14" t="s">
+      <c r="T4" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U4" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V4" s="2"/>
-      <c r="W4" s="14">
+      <c r="W4" s="13">
         <v>0</v>
       </c>
-      <c r="X4" s="14">
+      <c r="X4" s="13">
         <v>0</v>
       </c>
-      <c r="Y4" s="14">
+      <c r="Y4" s="13">
         <v>0</v>
       </c>
       <c r="Z4" s="2"/>
@@ -1422,20 +1415,20 @@
       <c r="M5" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N5" s="12"/>
-      <c r="O5" s="14" t="s">
+      <c r="N5" s="11"/>
+      <c r="O5" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P5" s="14" t="s">
+      <c r="P5" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q5" s="14" t="s">
+      <c r="Q5" s="13" t="s">
         <v>128</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="14" t="s">
+      <c r="T5" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U5" s="2" t="s">
@@ -1444,13 +1437,13 @@
       <c r="V5" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="W5" s="14">
-        <v>1</v>
-      </c>
-      <c r="X5" s="14">
+      <c r="W5" s="13">
+        <v>1</v>
+      </c>
+      <c r="X5" s="13">
         <v>3</v>
       </c>
-      <c r="Y5" s="14">
+      <c r="Y5" s="13">
         <v>1</v>
       </c>
       <c r="Z5" s="2"/>
@@ -1474,7 +1467,7 @@
       <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>136</v>
       </c>
       <c r="G6" t="s">
@@ -1493,20 +1486,20 @@
       <c r="M6" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N6" s="12"/>
-      <c r="O6" s="14" t="s">
+      <c r="N6" s="11"/>
+      <c r="O6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P6" s="14" t="s">
+      <c r="P6" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q6" s="14" t="s">
+      <c r="Q6" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="14" t="s">
+      <c r="T6" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U6" s="2" t="s">
@@ -1515,13 +1508,13 @@
       <c r="V6" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="W6" s="14">
-        <v>1</v>
-      </c>
-      <c r="X6" s="14">
+      <c r="W6" s="13">
+        <v>1</v>
+      </c>
+      <c r="X6" s="13">
         <v>2</v>
       </c>
-      <c r="Y6" s="14">
+      <c r="Y6" s="13">
         <v>1</v>
       </c>
       <c r="Z6" s="2"/>
@@ -1564,34 +1557,34 @@
       <c r="M7" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N7" s="12"/>
-      <c r="O7" s="14" t="s">
+      <c r="N7" s="11"/>
+      <c r="O7" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P7" s="14" t="s">
+      <c r="P7" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q7" s="14" t="s">
+      <c r="Q7" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S7" s="2"/>
-      <c r="T7" s="14" t="s">
+      <c r="T7" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U7" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V7" s="2"/>
-      <c r="W7" s="14">
-        <v>1</v>
-      </c>
-      <c r="X7" s="14">
+      <c r="W7" s="13">
+        <v>1</v>
+      </c>
+      <c r="X7" s="13">
         <v>2</v>
       </c>
-      <c r="Y7" s="14">
+      <c r="Y7" s="13">
         <v>1</v>
       </c>
       <c r="Z7" s="2"/>
@@ -1637,34 +1630,34 @@
       <c r="M8" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N8" s="12"/>
-      <c r="O8" s="14" t="s">
+      <c r="N8" s="11"/>
+      <c r="O8" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P8" s="14" t="s">
+      <c r="P8" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="Q8" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>14</v>
       </c>
       <c r="S8" s="2"/>
-      <c r="T8" s="14" t="s">
+      <c r="T8" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V8" s="2"/>
-      <c r="W8" s="14">
-        <v>1</v>
-      </c>
-      <c r="X8" s="14">
+      <c r="W8" s="13">
+        <v>1</v>
+      </c>
+      <c r="X8" s="13">
         <v>0</v>
       </c>
-      <c r="Y8" s="14">
+      <c r="Y8" s="13">
         <v>0</v>
       </c>
       <c r="Z8" s="2"/>
@@ -1710,34 +1703,34 @@
       <c r="M9" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N9" s="12"/>
-      <c r="O9" s="14" t="s">
+      <c r="N9" s="11"/>
+      <c r="O9" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P9" s="14" t="s">
+      <c r="P9" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q9" s="14" t="s">
+      <c r="Q9" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>14</v>
       </c>
       <c r="S9" s="2"/>
-      <c r="T9" s="14" t="s">
+      <c r="T9" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V9" s="2"/>
-      <c r="W9" s="14">
-        <v>1</v>
-      </c>
-      <c r="X9" s="14">
+      <c r="W9" s="13">
+        <v>1</v>
+      </c>
+      <c r="X9" s="13">
         <v>0</v>
       </c>
-      <c r="Y9" s="14">
+      <c r="Y9" s="13">
         <v>0</v>
       </c>
       <c r="Z9" s="2"/>
@@ -1783,21 +1776,21 @@
       <c r="M10" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N10" s="12"/>
-      <c r="O10" s="14" t="s">
+      <c r="N10" s="11"/>
+      <c r="O10" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P10" s="14" t="s">
+      <c r="P10" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q10" s="14" t="s">
+      <c r="Q10" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S10" s="2"/>
-      <c r="T10" s="14" t="s">
+      <c r="T10" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U10" s="2" t="s">
@@ -1806,13 +1799,13 @@
       <c r="V10" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="W10" s="14">
+      <c r="W10" s="13">
         <v>0</v>
       </c>
-      <c r="X10" s="14">
+      <c r="X10" s="13">
         <v>0</v>
       </c>
-      <c r="Y10" s="14">
+      <c r="Y10" s="13">
         <v>0</v>
       </c>
       <c r="Z10" s="2"/>
@@ -1860,21 +1853,21 @@
       <c r="M11" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N11" s="12"/>
-      <c r="O11" s="14" t="s">
+      <c r="N11" s="11"/>
+      <c r="O11" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P11" s="14" t="s">
+      <c r="P11" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q11" s="14" t="s">
+      <c r="Q11" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S11" s="2"/>
-      <c r="T11" s="14" t="s">
+      <c r="T11" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U11" s="2" t="s">
@@ -1883,13 +1876,13 @@
       <c r="V11" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="W11" s="14">
+      <c r="W11" s="13">
         <v>0</v>
       </c>
-      <c r="X11" s="14">
+      <c r="X11" s="13">
         <v>0</v>
       </c>
-      <c r="Y11" s="14">
+      <c r="Y11" s="13">
         <v>0</v>
       </c>
       <c r="Z11" s="2"/>
@@ -1937,34 +1930,34 @@
       <c r="M12" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N12" s="12"/>
-      <c r="O12" s="14" t="s">
+      <c r="N12" s="11"/>
+      <c r="O12" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P12" s="14" t="s">
+      <c r="P12" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q12" s="14" t="s">
+      <c r="Q12" s="13" t="s">
         <v>128</v>
       </c>
       <c r="R12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="S12" s="2"/>
-      <c r="T12" s="14" t="s">
+      <c r="T12" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U12" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V12" s="2"/>
-      <c r="W12" s="14">
-        <v>1</v>
-      </c>
-      <c r="X12" s="14">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="14">
+      <c r="W12" s="13">
+        <v>1</v>
+      </c>
+      <c r="X12" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="13">
         <v>0</v>
       </c>
       <c r="Z12" s="2"/>
@@ -2012,14 +2005,14 @@
       <c r="M13" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N13" s="12"/>
-      <c r="O13" s="14" t="s">
+      <c r="N13" s="11"/>
+      <c r="O13" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P13" s="14" t="s">
+      <c r="P13" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q13" s="14" t="s">
+      <c r="Q13" s="13" t="s">
         <v>116</v>
       </c>
       <c r="R13" s="2" t="s">
@@ -2028,20 +2021,20 @@
       <c r="S13" s="2">
         <v>20</v>
       </c>
-      <c r="T13" s="14" t="s">
+      <c r="T13" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U13" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V13" s="2"/>
-      <c r="W13" s="14">
+      <c r="W13" s="13">
         <v>0</v>
       </c>
-      <c r="X13" s="14">
+      <c r="X13" s="13">
         <v>0</v>
       </c>
-      <c r="Y13" s="14">
+      <c r="Y13" s="13">
         <v>0</v>
       </c>
       <c r="Z13" s="2"/>
@@ -2091,14 +2084,14 @@
       <c r="M14" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N14" s="12"/>
-      <c r="O14" s="14" t="s">
+      <c r="N14" s="11"/>
+      <c r="O14" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P14" s="14" t="s">
+      <c r="P14" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q14" s="14" t="s">
+      <c r="Q14" s="13" t="s">
         <v>116</v>
       </c>
       <c r="R14" s="2" t="s">
@@ -2107,7 +2100,7 @@
       <c r="S14" s="2">
         <v>20</v>
       </c>
-      <c r="T14" s="14" t="s">
+      <c r="T14" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U14" s="2" t="s">
@@ -2116,13 +2109,13 @@
       <c r="V14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="W14" s="14">
+      <c r="W14" s="13">
         <v>0</v>
       </c>
-      <c r="X14" s="14">
+      <c r="X14" s="13">
         <v>0</v>
       </c>
-      <c r="Y14" s="14">
+      <c r="Y14" s="13">
         <v>0</v>
       </c>
       <c r="Z14" s="2"/>
@@ -2172,34 +2165,34 @@
       <c r="M15" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="N15" s="12"/>
-      <c r="O15" s="14" t="s">
+      <c r="N15" s="11"/>
+      <c r="O15" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="P15" s="14" t="s">
+      <c r="P15" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="Q15" s="14" t="s">
+      <c r="Q15" s="13" t="s">
         <v>115</v>
       </c>
       <c r="R15" s="2" t="s">
         <v>5</v>
       </c>
       <c r="S15" s="2"/>
-      <c r="T15" s="14" t="s">
+      <c r="T15" s="13" t="s">
         <v>120</v>
       </c>
       <c r="U15" s="2" t="s">
         <v>121</v>
       </c>
       <c r="V15" s="2"/>
-      <c r="W15" s="14">
-        <v>1</v>
-      </c>
-      <c r="X15" s="14">
+      <c r="W15" s="13">
+        <v>1</v>
+      </c>
+      <c r="X15" s="13">
         <v>2</v>
       </c>
-      <c r="Y15" s="14">
+      <c r="Y15" s="13">
         <v>0</v>
       </c>
       <c r="Z15" s="2"/>
@@ -2589,10 +2582,10 @@
       <c r="G1" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="10" t="s">
         <v>106</v>
       </c>
       <c r="J1" s="7" t="s">
@@ -2604,16 +2597,16 @@
       <c r="L1" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="O1" s="10" t="s">
+      <c r="O1" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="P1" s="10" t="s">
+      <c r="P1" s="9" t="s">
         <v>112</v>
       </c>
       <c r="Q1" s="7" t="s">
@@ -2622,10 +2615,10 @@
       <c r="R1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="9" t="s">
         <v>118</v>
       </c>
       <c r="U1" s="7" t="s">
@@ -2637,13 +2630,13 @@
       <c r="W1" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="X1" s="10" t="s">
+      <c r="X1" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="Y1" s="10" t="s">
+      <c r="Y1" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="Z1" s="10" t="s">
+      <c r="Z1" s="9" t="s">
         <v>124</v>
       </c>
       <c r="AA1" s="7" t="s">
@@ -2690,36 +2683,36 @@
       <c r="L2" s="4" t="b">
         <v>1</v>
       </c>
-      <c r="M2" s="12"/>
-      <c r="N2" s="14" t="s">
+      <c r="M2" s="11"/>
+      <c r="N2" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="13" t="s">
         <v>116</v>
       </c>
       <c r="Q2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S2" s="14" t="s">
+      <c r="S2" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="T2" s="14" t="s">
+      <c r="T2" s="13" t="s">
         <v>121</v>
       </c>
       <c r="V2" s="2"/>
       <c r="W2" s="2">
         <v>28397686</v>
       </c>
-      <c r="X2" s="14">
+      <c r="X2" s="13">
         <v>0</v>
       </c>
-      <c r="Y2" s="14">
+      <c r="Y2" s="13">
         <v>0</v>
       </c>
-      <c r="Z2" s="14">
+      <c r="Z2" s="13">
         <v>0</v>
       </c>
       <c r="AA2" s="2"/>

--- a/tabular/reference/sublineage/herv_sublineage_data.xlsx
+++ b/tabular/reference/sublineage/herv_sublineage_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rob/Projects/erv/locus-level/ERVdb-HomoSapiens/tabular/reference/sublineage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{895E8C8F-3ECD-E046-A189-EBA3B96E6B05}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ADE3F02-3D45-7043-8915-AB1C5668936B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="940" yWindow="500" windowWidth="27380" windowHeight="10840" xr2:uid="{86B1DAFB-2671-1448-A19A-2233561734CB}"/>
   </bookViews>
@@ -452,7 +452,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -490,12 +490,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Unicode MS"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -542,7 +536,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -573,7 +567,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1451,7 +1444,7 @@
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
     </row>
-    <row r="6" spans="1:29" ht="17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>61</v>
       </c>
@@ -1467,7 +1460,7 @@
       <c r="E6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="2" t="s">
         <v>136</v>
       </c>
       <c r="G6" t="s">
